--- a/data/thesis_outputs/figures/FIGURE_3.xlsx
+++ b/data/thesis_outputs/figures/FIGURE_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SOURCE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CHART_DATA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CHART_SPEC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHART_DATA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHART_SPEC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -1809,14 +1809,14 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>{"reason": "No contract-approved exact source_path/x/series mapping; arbitrary first-column auto-charting is prohibited.", "status": "EDITABLE_SPEC_ONLY"}</t>
+          <t>{"reason": "Editable diagram item based on the listed evidence paths and layout specification.", "status": "EDITABLE_SPEC_ONLY"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>한계·설명</t>
+          <t>해석·설명</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>이 시트의 텍스트와 근거 경로를 사용해 도식 또는 그림을 편집합니다. 경험적 결과가 없는 경우 수치를 임의로 만들지 않습니다.</t>
+          <t>이 시트의 텍스트와 근거 경로를 사용해 도식 또는 그림을 편집합니다. 경험적 결과가 없는 항목은 설계 근거로 표시합니다.</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>재생성 주장</t>
+          <t>자료 구분</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>하지 않음</t>
+          <t>설계 근거 또는 preserved evidence</t>
         </is>
       </c>
     </row>
